--- a/artfynd/A 23875-2026 artfynd.xlsx
+++ b/artfynd/A 23875-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134835119</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134835122</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134835115</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134835109</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134835110</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134835114</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134835116</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134835117</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134835125</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134835129</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,6 +1904,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134835134</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1965,6 +2025,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134835108</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2085,6 +2150,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134835113</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2205,6 +2275,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134835120</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2325,6 +2400,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134835121</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2445,6 +2525,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134835132</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2565,6 +2650,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134835111</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2685,6 +2775,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134835112</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2805,6 +2900,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134835124</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2920,6 +3020,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134835130</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3040,6 +3145,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134835131</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3160,6 +3270,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134835133</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3267,8 +3382,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134835127</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 23875-2026 artfynd.xlsx
+++ b/artfynd/A 23875-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134835119</v>
       </c>
       <c r="B2" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>134835122</v>
       </c>
       <c r="B3" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>134835115</v>
       </c>
       <c r="B4" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 23875-2026 artfynd.xlsx
+++ b/artfynd/A 23875-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134835119</v>
       </c>
       <c r="B2" t="n">
-        <v>92046</v>
+        <v>92060</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>134835122</v>
       </c>
       <c r="B3" t="n">
-        <v>92046</v>
+        <v>92060</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>134835115</v>
       </c>
       <c r="B4" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>134835109</v>
       </c>
       <c r="B5" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>134835110</v>
       </c>
       <c r="B6" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>134835114</v>
       </c>
       <c r="B7" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>134835116</v>
       </c>
       <c r="B8" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>134835117</v>
       </c>
       <c r="B9" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>134835125</v>
       </c>
       <c r="B10" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>134835129</v>
       </c>
       <c r="B11" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>134835134</v>
       </c>
       <c r="B12" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>134835108</v>
       </c>
       <c r="B13" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>134835113</v>
       </c>
       <c r="B14" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>134835120</v>
       </c>
       <c r="B15" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>134835121</v>
       </c>
       <c r="B16" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>134835132</v>
       </c>
       <c r="B17" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>134835111</v>
       </c>
       <c r="B18" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>134835112</v>
       </c>
       <c r="B19" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>134835124</v>
       </c>
       <c r="B20" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>134835130</v>
       </c>
       <c r="B21" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>134835131</v>
       </c>
       <c r="B22" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>134835133</v>
       </c>
       <c r="B23" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         <v>134835127</v>
       </c>
       <c r="B24" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 23875-2026 artfynd.xlsx
+++ b/artfynd/A 23875-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134835119</v>
       </c>
       <c r="B2" t="n">
-        <v>92060</v>
+        <v>92061</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>134835122</v>
       </c>
       <c r="B3" t="n">
-        <v>92060</v>
+        <v>92061</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>134835115</v>
       </c>
       <c r="B4" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>134835109</v>
       </c>
       <c r="B5" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>134835110</v>
       </c>
       <c r="B6" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>134835114</v>
       </c>
       <c r="B7" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>134835116</v>
       </c>
       <c r="B8" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>134835117</v>
       </c>
       <c r="B9" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>134835125</v>
       </c>
       <c r="B10" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>134835129</v>
       </c>
       <c r="B11" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>134835134</v>
       </c>
       <c r="B12" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         <v>134835127</v>
       </c>
       <c r="B24" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 23875-2026 artfynd.xlsx
+++ b/artfynd/A 23875-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134835119</v>
       </c>
       <c r="B2" t="n">
-        <v>92061</v>
+        <v>92062</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>134835122</v>
       </c>
       <c r="B3" t="n">
-        <v>92061</v>
+        <v>92062</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>134835115</v>
       </c>
       <c r="B4" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
